--- a/hpi_scraper/JobsHiring/coresignal/coresignal_api_report.xlsx
+++ b/hpi_scraper/JobsHiring/coresignal/coresignal_api_report.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>12.707 avg</t>
+          <t>14.435 avg</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>92</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">

--- a/hpi_scraper/JobsHiring/coresignal/coresignal_api_report.xlsx
+++ b/hpi_scraper/JobsHiring/coresignal/coresignal_api_report.xlsx
@@ -449,15 +449,15 @@
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="49" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="66" customWidth="1" min="5" max="5"/>
+    <col width="72" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="19" customWidth="1" min="12" max="12"/>
-    <col width="70" customWidth="1" min="13" max="13"/>
+    <col width="72" customWidth="1" min="11" max="11"/>
+    <col width="72" customWidth="1" min="12" max="12"/>
+    <col width="72" customWidth="1" min="13" max="13"/>
     <col width="24" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -556,7 +556,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Estimated 3 search credits + 10 collect credits</t>
+          <t>3 search requests plus 10 collected job records for Sea Limited.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -564,15 +564,11 @@
           <t>ratelimit-limit: 18; ratelimit-remaining: 17; ratelimit-reset: 1; x-ratelimit-limit-second: 18; x-ratelimit-remaining-second: 17</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="G2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
@@ -586,17 +582,17 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>92 total postings signalled; 10 job detail records collected for sample fields.</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>No - counts, Singapore count, role grouping, locations, first-seen dates and source URLs were populated.</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>Coresignal Jobs API search provides counts; collect endpoint provides job-level location, date, and source URL.</t>
+          <t>Best jobs/hiring source in this run. It supplied the broadest usable job count and enough collected postings for location and role evidence.</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
